--- a/cleaned_data.xlsx
+++ b/cleaned_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/helioribeiro/Documents/03_WORK/01_UCLOUD/01_REPOSITORIOS/text2sql-vertex/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56C30AC-902A-324D-88D2-C1583726EEEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB0FCB6-67C2-B042-89A8-AD869A6EDF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -484,6 +484,18 @@
 ORDER BY MES DESC</t>
   </si>
   <si>
+    <t>What are the 100 most sold products in a year?</t>
+  </si>
+  <si>
+    <t>What are the 10 most sold products per month?</t>
+  </si>
+  <si>
+    <t>What is the sales growth rate of each salesperson per year?</t>
+  </si>
+  <si>
+    <t>Simple Search</t>
+  </si>
+  <si>
     <t>WITH agg AS (
   SELECT
   EXTRACT(YEAR FROM  DATA) AS YEAR_RAW,
@@ -497,20 +509,8 @@
   VENDAS_RAW AS VENDAS,
   VENDEDOR_RAW AS VENDEDOR,
   LEAD(VENDAS_RAW) OVER (Partition BY VENDEDOR_RAW ORDER BY YEAR_RAW DESC) as VENDA_ANO_PASSADO,
-  ROUND(100*(VENDAS_RAW -  LEAD(VENDAS_RAW) OVER (Partition BY VENDEDOR_RAW ORDER BY YEAR_RAW DESC))/(LEAD(VENDAS_RAW) OVER (Partition BY VENDEDOR_RAW ORDER BY MES_YEAR_RAWRAW DESC)),2) as TAXA_CRESCIMENTO
+  ROUND(100*(VENDAS_RAW -  LEAD(VENDAS_RAW) OVER (Partition BY VENDEDOR_RAW ORDER BY YEAR_RAW DESC))/(LEAD(VENDAS_RAW) OVER (Partition BY VENDEDOR_RAW ORDER BY YEAR_RAW DESC)),2) as TAXA_CRESCIMENTO
 FROM agg</t>
-  </si>
-  <si>
-    <t>What are the 100 most sold products in a year?</t>
-  </si>
-  <si>
-    <t>What are the 10 most sold products per month?</t>
-  </si>
-  <si>
-    <t>What is the sales growth rate of each salesperson per year?</t>
-  </si>
-  <si>
-    <t>Simple Search</t>
   </si>
 </sst>
 </file>
@@ -1437,7 +1437,7 @@
         <v>10</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>61</v>
@@ -1463,7 +1463,7 @@
         <v>54</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>64</v>
@@ -1486,13 +1486,13 @@
         <v>54</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="389" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="373" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>7</v>
       </c>
@@ -1509,10 +1509,10 @@
         <v>54</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
